--- a/ig/mc-changes/StructureDefinition-as-device.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="404">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T12:40:41+00:00</t>
+    <t>2023-05-09T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -457,10 +457,13 @@
 </t>
   </si>
   <si>
-    <t>numeroAutorisationARHGOS</t>
-  </si>
-  <si>
     <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de l'identifiant métier de l'autorisation ARHGOS d’un équipement matériel lourd.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t>Device.extension:as-ext-device-authorization-date-device</t>
@@ -473,10 +476,10 @@
 </t>
   </si>
   <si>
-    <t>dateDecision</t>
-  </si>
-  <si>
     <t>Date de délivrance de l’autorisation d’EML.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la date de délivrance de l’autorisation d’un équipement matériel lourd.</t>
   </si>
   <si>
     <t>Synonyme FINESS : date d’autorisation.</t>
@@ -522,9 +525,6 @@
   </si>
   <si>
     <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
-  </si>
-  <si>
-    <t>Synonyme MOS : numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t>.id</t>
@@ -2682,7 +2682,9 @@
       <c r="M10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -2757,13 +2759,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>74</v>
@@ -2785,16 +2787,16 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2870,13 +2872,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>74</v>
@@ -2898,13 +2900,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2981,10 +2983,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3010,16 +3012,16 @@
         <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>74</v>
@@ -3068,7 +3070,7 @@
         <v>135</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -3094,10 +3096,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3120,16 +3122,16 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3179,7 +3181,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3685,7 +3687,7 @@
         <v>132</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
@@ -5681,7 +5683,7 @@
         <v>132</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -6678,7 +6680,7 @@
         <v>132</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
@@ -7342,7 +7344,7 @@
         <v>132</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
@@ -7554,7 +7556,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>333</v>
@@ -8115,7 +8117,7 @@
         <v>132</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>74</v>

--- a/ig/mc-changes/StructureDefinition-as-device.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T14:30:45+00:00</t>
+    <t>2023-05-09T15:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-changes/StructureDefinition-as-device.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-device.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-device</t>
+    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-device</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:20:28+00:00</t>
+    <t>2023-05-09T16:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -453,7 +453,7 @@
     <t>as-ext-device-number-authorization-arhgos</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-number-authorization-arhgos}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-number-authorization-arhgos}
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>as-ext-device-authorization-date-device</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-authorization-date-device}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-authorization-date-device}
 </t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>as-ext-device-Period-implantation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-Period-implantation}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-Period-implantation}
 </t>
   </si>
   <si>
@@ -1172,7 +1172,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -1611,7 +1611,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="159.0546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="142.90234375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/mc-changes/StructureDefinition-as-device.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T16:25:19+00:00</t>
+    <t>2023-05-16T15:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-changes/StructureDefinition-as-device.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-device.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="450">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-device</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-device</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.3</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>As Device Profile</t>
+    <t>AS Device Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-16T15:53:03+00:00</t>
+    <t>2023-06-08T09:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de la ressource Device dans le contexte de l'Annuaire Santé pour décrire les équipements matériels lourds ('EML') mis en oeuvre au sein d'un établissement.</t>
+    <t>Profil créé à partir de Device dans le contexte de l'Annuaire Santé pour décrire les équipements matériels lourds ('EML') mis en oeuvre au sein d'un établissement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -304,20 +304,216 @@
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Device.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Device.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Device.meta.extension:as-data-trace</t>
+  </si>
+  <si>
+    <t>as-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace</t>
+  </si>
+  <si>
+    <t>Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI))..</t>
+  </si>
+  <si>
+    <t>Device.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Device.implicitRules</t>
+    <t>Device.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Device.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Device.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Device.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Device.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Device.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -328,9 +524,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Device.language</t>
@@ -413,69 +606,41 @@
     <t>Device.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Device.extension:as-ext-device-number-authorization-arhgos</t>
+  </si>
+  <si>
+    <t>as-ext-device-number-authorization-arhgos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-number-authorization-arhgos}
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de l'identifiant métier de l'autorisation ARHGOS d’un équipement matériel lourd.</t>
+  </si>
+  <si>
+    <t>Synonyme : numeroAutorisationARHGOS</t>
+  </si>
+  <si>
+    <t>Device.extension:as-ext-device-authorization-date-device</t>
+  </si>
+  <si>
+    <t>as-ext-device-authorization-date-device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-authorization-date-device}
 </t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Device.extension:as-ext-device-number-authorization-arhgos</t>
-  </si>
-  <si>
-    <t>as-ext-device-number-authorization-arhgos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-number-authorization-arhgos}
-</t>
-  </si>
-  <si>
-    <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML.</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de l'identifiant métier de l'autorisation ARHGOS d’un équipement matériel lourd.</t>
-  </si>
-  <si>
-    <t>Synonyme MOS : numeroAutorisationARHGOS</t>
-  </si>
-  <si>
-    <t>Device.extension:as-ext-device-authorization-date-device</t>
-  </si>
-  <si>
-    <t>as-ext-device-authorization-date-device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-authorization-date-device}
-</t>
-  </si>
-  <si>
     <t>Date de délivrance de l’autorisation d’EML.</t>
   </si>
   <si>
@@ -491,7 +656,7 @@
     <t>as-ext-device-Period-implantation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-Period-implantation}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-device-Period-implantation}
 </t>
   </si>
   <si>
@@ -581,26 +746,7 @@
     <t>Device.udiCarrier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Device.udiCarrier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -805,9 +951,6 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>The availability status reason of the device.</t>
   </si>
   <si>
@@ -906,7 +1049,7 @@
     <t>The serial number assigned by the organization when the device was manufactured.</t>
   </si>
   <si>
-    <t>Synonyme MOS : numeroSerie</t>
+    <t>Synonyme : numeroSerie</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].id</t>
@@ -995,7 +1138,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>Synonyme MOS : equipementMaterielLourd</t>
+    <t>Synonyme : equipementMaterielLourd</t>
   </si>
   <si>
     <t>Liste des types d'EML</t>
@@ -1172,7 +1315,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -1182,7 +1325,7 @@
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idStructure</t>
+    <t>Synonyme : idStructure</t>
   </si>
   <si>
     <t>.playedRole[typeCode=OWN].scoper</t>
@@ -1598,7 +1741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.40625" customWidth="true" bestFit="true"/>
@@ -1611,7 +1754,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="142.90234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="143.859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1625,7 +1768,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="42.08203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="112.0078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2077,10 +2220,10 @@
         <v>93</v>
       </c>
       <c r="AJ4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>74</v>
@@ -2091,10 +2234,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2111,23 +2254,21 @@
         <v>74</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="M5" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>100</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>74</v>
@@ -2176,7 +2317,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -2185,13 +2326,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>74</v>
@@ -2202,21 +2343,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -2228,16 +2369,16 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2263,46 +2404,46 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AC6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>74</v>
@@ -2316,11 +2457,13 @@
         <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2330,7 +2473,7 @@
         <v>81</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>74</v>
@@ -2347,9 +2490,7 @@
       <c r="M7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="N7" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>74</v>
@@ -2398,22 +2539,22 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>74</v>
@@ -2424,21 +2565,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -2447,19 +2588,19 @@
         <v>74</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2509,22 +2650,22 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>74</v>
@@ -2535,21 +2676,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -2558,19 +2699,19 @@
         <v>74</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2608,34 +2749,34 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>74</v>
@@ -2646,14 +2787,12 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2665,25 +2804,25 @@
         <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2733,22 +2872,22 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>74</v>
@@ -2759,14 +2898,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2775,28 +2912,28 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2846,7 +2983,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2858,10 +2995,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>74</v>
@@ -2872,14 +3009,12 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
@@ -2888,27 +3023,29 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
@@ -2933,13 +3070,13 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2957,7 +3094,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2969,10 +3106,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>74</v>
@@ -2983,14 +3120,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3003,26 +3140,24 @@
         <v>74</v>
       </c>
       <c r="I13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="J13" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
@@ -3046,31 +3181,31 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -3082,10 +3217,10 @@
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>74</v>
@@ -3096,10 +3231,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3110,28 +3245,28 @@
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3181,36 +3316,36 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>165</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3233,16 +3368,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3268,13 +3403,13 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -3292,7 +3427,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3304,10 +3439,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -3325,14 +3460,14 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -3341,19 +3476,19 @@
         <v>74</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3403,25 +3538,25 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>74</v>
@@ -3429,21 +3564,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -3455,15 +3590,17 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -3512,13 +3649,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -3527,7 +3664,7 @@
         <v>74</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>74</v>
@@ -3538,14 +3675,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3564,16 +3701,16 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3611,19 +3748,19 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3635,10 +3772,10 @@
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>74</v>
@@ -3649,46 +3786,46 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>74</v>
       </c>
@@ -3736,7 +3873,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3748,10 +3885,10 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>74</v>
@@ -3762,14 +3899,16 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3779,25 +3918,25 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3847,40 +3986,42 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>199</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3890,7 +4031,7 @@
         <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3899,17 +4040,15 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
@@ -3958,71 +4097,71 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>206</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>74</v>
@@ -4059,34 +4198,34 @@
         <v>74</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>74</v>
@@ -4097,42 +4236,42 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4182,25 +4321,25 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>218</v>
@@ -4215,7 +4354,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>220</v>
+        <v>74</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4231,10 +4370,10 @@
         <v>74</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>221</v>
@@ -4305,24 +4444,24 @@
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>94</v>
+        <v>224</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>224</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4333,7 +4472,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -4342,23 +4481,21 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
       </c>
@@ -4382,13 +4519,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>231</v>
+        <v>74</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4406,25 +4543,25 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>74</v>
@@ -4432,10 +4569,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4449,26 +4586,24 @@
         <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>97</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
@@ -4493,13 +4628,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>237</v>
+        <v>74</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4517,7 +4652,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4526,16 +4661,16 @@
         <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>74</v>
@@ -4543,14 +4678,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4569,16 +4704,16 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>104</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>245</v>
+        <v>106</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4604,31 +4739,31 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>248</v>
+        <v>74</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4640,13 +4775,13 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AK27" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="AL27" t="s" s="2">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>74</v>
@@ -4654,44 +4789,46 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>74</v>
       </c>
@@ -4739,40 +4876,40 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AK28" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="AL28" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>256</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>74</v>
+        <v>240</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4782,25 +4919,25 @@
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4850,7 +4987,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4862,28 +4999,28 @@
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>95</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4902,15 +5039,17 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>263</v>
+        <v>130</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
@@ -4959,7 +5098,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4971,24 +5110,24 @@
         <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5011,16 +5150,20 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>263</v>
+        <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>74</v>
       </c>
@@ -5068,7 +5211,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5080,28 +5223,28 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>272</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5117,19 +5260,19 @@
         <v>74</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5179,7 +5322,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5191,28 +5334,28 @@
         <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5222,25 +5365,25 @@
         <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5290,7 +5433,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5302,24 +5445,24 @@
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>74</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5330,7 +5473,7 @@
         <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>74</v>
@@ -5342,16 +5485,20 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>74</v>
       </c>
@@ -5375,13 +5522,13 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>74</v>
+        <v>276</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>74</v>
+        <v>277</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -5399,22 +5546,22 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>74</v>
@@ -5425,10 +5572,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5442,24 +5589,26 @@
         <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>181</v>
+        <v>281</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -5484,13 +5633,13 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>74</v>
+        <v>276</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>74</v>
+        <v>284</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -5508,7 +5657,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>183</v>
+        <v>280</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5517,16 +5666,16 @@
         <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>74</v>
@@ -5534,14 +5683,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5560,16 +5709,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>129</v>
+        <v>289</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>132</v>
+        <v>292</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5595,31 +5744,31 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>74</v>
+        <v>294</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5631,13 +5780,13 @@
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>74</v>
@@ -5645,46 +5794,44 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>188</v>
+        <v>297</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>299</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -5732,50 +5879,50 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>74</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5784,16 +5931,16 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>196</v>
+        <v>306</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5843,10 +5990,10 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>81</v>
@@ -5855,24 +6002,24 @@
         <v>93</v>
       </c>
       <c r="AJ38" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5880,7 +6027,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>81</v>
@@ -5895,17 +6042,15 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>309</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5930,13 +6075,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>294</v>
+        <v>74</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>295</v>
+        <v>74</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5954,10 +6099,10 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>81</v>
@@ -5966,24 +6111,24 @@
         <v>93</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>74</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6006,17 +6151,15 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>180</v>
+        <v>309</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>74</v>
@@ -6065,7 +6208,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6077,24 +6220,24 @@
         <v>93</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>74</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6117,16 +6260,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6176,7 +6319,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6188,24 +6331,24 @@
         <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>74</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6228,16 +6371,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>242</v>
+        <v>96</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6263,13 +6406,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>309</v>
+        <v>74</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>310</v>
+        <v>74</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -6287,7 +6430,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -6299,13 +6442,13 @@
         <v>93</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>249</v>
+        <v>326</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>74</v>
@@ -6313,10 +6456,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6339,13 +6482,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>174</v>
+        <v>227</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6396,7 +6539,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6408,10 +6551,10 @@
         <v>93</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>74</v>
@@ -6422,10 +6565,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6448,13 +6591,13 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>181</v>
+        <v>97</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6505,7 +6648,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>183</v>
+        <v>99</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6520,7 +6663,7 @@
         <v>74</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>74</v>
@@ -6531,14 +6674,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6557,16 +6700,16 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6604,19 +6747,19 @@
         <v>74</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6628,10 +6771,10 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>74</v>
@@ -6642,14 +6785,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6668,19 +6811,19 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>158</v>
+        <v>211</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
@@ -6729,7 +6872,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6741,10 +6884,10 @@
         <v>93</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>74</v>
@@ -6755,14 +6898,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6781,16 +6924,16 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>242</v>
+        <v>96</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6840,7 +6983,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6852,10 +6995,10 @@
         <v>93</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>74</v>
@@ -6866,10 +7009,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6877,7 +7020,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>81</v>
@@ -6892,16 +7035,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6927,13 +7070,13 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>74</v>
+        <v>276</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>74</v>
+        <v>340</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>74</v>
+        <v>341</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6951,10 +7094,10 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>81</v>
@@ -6963,13 +7106,13 @@
         <v>93</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>102</v>
+        <v>342</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>74</v>
@@ -6977,10 +7120,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6991,7 +7134,7 @@
         <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -7003,15 +7146,17 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>74</v>
@@ -7060,25 +7205,25 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>102</v>
+        <v>346</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>74</v>
@@ -7086,10 +7231,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7112,15 +7257,17 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>181</v>
+        <v>348</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -7169,7 +7316,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>183</v>
+        <v>347</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7178,16 +7325,16 @@
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>74</v>
@@ -7195,24 +7342,24 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -7221,16 +7368,16 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>129</v>
+        <v>289</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>130</v>
+        <v>352</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>132</v>
+        <v>354</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7256,46 +7403,46 @@
         <v>74</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>74</v>
+        <v>276</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>74</v>
+        <v>355</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>74</v>
+        <v>356</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>186</v>
+        <v>351</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>74</v>
@@ -7306,14 +7453,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7326,26 +7473,22 @@
         <v>74</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>129</v>
+        <v>227</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>189</v>
+        <v>358</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -7393,7 +7536,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>191</v>
+        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7405,10 +7548,10 @@
         <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>74</v>
@@ -7419,14 +7562,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7445,17 +7588,15 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>242</v>
+        <v>96</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>330</v>
+        <v>97</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>74</v>
@@ -7504,7 +7645,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>99</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7513,13 +7654,13 @@
         <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
@@ -7530,21 +7671,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -7556,15 +7697,17 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>333</v>
+        <v>104</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>74</v>
@@ -7601,37 +7744,37 @@
         <v>74</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>332</v>
+        <v>110</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ54" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK54" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AK54" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AL54" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>74</v>
@@ -7639,44 +7782,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>74</v>
       </c>
@@ -7724,22 +7869,22 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK55" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>74</v>
@@ -7750,21 +7895,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -7776,15 +7921,17 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>174</v>
+        <v>289</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
@@ -7833,22 +7980,22 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>74</v>
@@ -7859,10 +8006,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7885,15 +8032,17 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>181</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>74</v>
@@ -7942,7 +8091,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7951,16 +8100,16 @@
         <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>74</v>
@@ -7968,14 +8117,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7994,17 +8143,15 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>227</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>74</v>
@@ -8041,19 +8188,19 @@
         <v>74</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>186</v>
+        <v>369</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8065,10 +8212,10 @@
         <v>93</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>74</v>
@@ -8079,46 +8226,42 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>74</v>
       </c>
@@ -8166,22 +8309,22 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>191</v>
+        <v>99</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>74</v>
@@ -8192,21 +8335,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
@@ -8218,16 +8361,16 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>242</v>
+        <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>346</v>
+        <v>104</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>347</v>
+        <v>105</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>245</v>
+        <v>106</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8265,34 +8408,34 @@
         <v>74</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>345</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK60" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8303,14 +8446,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8323,24 +8466,26 @@
         <v>74</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>349</v>
+        <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>350</v>
+        <v>236</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>351</v>
+        <v>237</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>74</v>
       </c>
@@ -8388,7 +8533,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>348</v>
+        <v>238</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8400,10 +8545,10 @@
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>353</v>
+        <v>111</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>354</v>
+        <v>94</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
@@ -8414,21 +8559,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8440,16 +8585,16 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8499,22 +8644,22 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>74</v>
@@ -8525,10 +8670,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8551,20 +8696,16 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>359</v>
+        <v>214</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>74</v>
       </c>
@@ -8612,7 +8753,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8624,13 +8765,13 @@
         <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>364</v>
+        <v>245</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>74</v>
@@ -8638,10 +8779,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8649,13 +8790,13 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8664,16 +8805,16 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>366</v>
+        <v>96</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>369</v>
+        <v>243</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8723,10 +8864,10 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>81</v>
@@ -8735,13 +8876,13 @@
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>371</v>
+        <v>74</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
@@ -8749,10 +8890,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8775,17 +8916,15 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>373</v>
+        <v>227</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>74</v>
@@ -8834,7 +8973,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8846,13 +8985,13 @@
         <v>93</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>377</v>
+        <v>122</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>378</v>
+        <v>100</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>371</v>
+        <v>74</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>74</v>
@@ -8860,10 +8999,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8886,20 +9025,16 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>380</v>
+        <v>96</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>381</v>
+        <v>97</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>74</v>
       </c>
@@ -8947,7 +9082,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>99</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -8956,16 +9091,16 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>171</v>
+        <v>74</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>384</v>
+        <v>100</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>385</v>
+        <v>74</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>74</v>
@@ -8973,21 +9108,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>74</v>
@@ -8999,16 +9134,16 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>387</v>
+        <v>104</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>388</v>
+        <v>105</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>389</v>
+        <v>106</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9046,37 +9181,37 @@
         <v>74</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>386</v>
+        <v>110</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ67" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK67" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AK67" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AL67" t="s" s="2">
-        <v>385</v>
+        <v>74</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
@@ -9084,14 +9219,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9104,24 +9239,26 @@
         <v>74</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>392</v>
+        <v>103</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>393</v>
+        <v>236</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>394</v>
+        <v>237</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>74</v>
       </c>
@@ -9169,7 +9306,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>391</v>
+        <v>238</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9181,10 +9318,10 @@
         <v>93</v>
       </c>
       <c r="AJ68" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>74</v>
@@ -9195,10 +9332,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9206,10 +9343,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -9218,19 +9355,19 @@
         <v>74</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9280,22 +9417,22 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>232</v>
+        <v>295</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9306,10 +9443,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9320,7 +9457,7 @@
         <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -9332,16 +9469,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>170</v>
+        <v>398</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9391,32 +9528,1035 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>171</v>
+        <v>399</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>172</v>
+        <v>400</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM70">
+  <autoFilter ref="A1:AM79">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9426,7 +10566,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
